--- a/data/result_sens_mk.xlsx
+++ b/data/result_sens_mk.xlsx
@@ -516,52 +516,52 @@
         <v>0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8758524834198476</v>
+        <v>0.8034193717709648</v>
       </c>
       <c r="D2" t="n">
-        <v>0.922162141009142</v>
+        <v>0.8921940582609267</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5934758101529934</v>
+        <v>0.5089717394212293</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7252544192152204</v>
+        <v>0.657250568789626</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6621736856750758</v>
+        <v>0.6143208736150618</v>
       </c>
       <c r="H2" t="n">
-        <v>0.792870107428044</v>
+        <v>0.7887538216701685</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3832364568849448</v>
+        <v>0.3044020289837863</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5918987279176325</v>
+        <v>0.5208605530389908</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6159188306065855</v>
+        <v>0.5791091306271914</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7556319630272135</v>
+        <v>0.760732682204998</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3978482196720919</v>
+        <v>0.3186619481052885</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5980866382986938</v>
+        <v>0.5302690807032707</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8148576217909003</v>
+        <v>0.7485175188813785</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8820231977229795</v>
+        <v>0.8596010522567237</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.55570322486028</v>
+        <v>0.463071429848682</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6959593488539626</v>
+        <v>0.6236212873234698</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +572,52 @@
         <v>0.2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9064767701863798</v>
+        <v>0.8404762115636063</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9522625832604751</v>
+        <v>0.9305278824970453</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7476692752483987</v>
+        <v>0.6566852471224521</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8534433794883435</v>
+        <v>0.7912866773455448</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8373022414856306</v>
+        <v>0.7766223122856062</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9154545937729722</v>
+        <v>0.9011222874553728</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5880476871669202</v>
+        <v>0.4755550463096773</v>
       </c>
       <c r="J3" t="n">
-        <v>0.749978483328088</v>
+        <v>0.6723818121842717</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8025900157242186</v>
+        <v>0.7481668318735715</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8919152806836386</v>
+        <v>0.883394293310108</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5975693151592639</v>
+        <v>0.4908320011664796</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7601875921928595</v>
+        <v>0.6844706465917753</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8867951805645001</v>
+        <v>0.8229029140327412</v>
       </c>
       <c r="P3" t="n">
-        <v>0.940576264347988</v>
+        <v>0.9214147992220197</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7234699114477606</v>
+        <v>0.6219244589880911</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8354233822136937</v>
+        <v>0.7663778731794469</v>
       </c>
     </row>
     <row r="4">
@@ -628,52 +628,52 @@
         <v>0.3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9346926209316726</v>
+        <v>0.8741155386680298</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9701958521518353</v>
+        <v>0.9512655466976991</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8334573209985008</v>
+        <v>0.7496164055121965</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9087345578533064</v>
+        <v>0.8555027558527853</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9060952650333105</v>
+        <v>0.8456215931541946</v>
       </c>
       <c r="H4" t="n">
-        <v>0.956168988539062</v>
+        <v>0.9393131131543758</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7049757425130065</v>
+        <v>0.5878163660842636</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8249913193172764</v>
+        <v>0.7503870628981028</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8851331231636511</v>
+        <v>0.8279372125867632</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9436515924713396</v>
+        <v>0.9301342419257631</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7107052918193513</v>
+        <v>0.5994394709210434</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8339182756550685</v>
+        <v>0.7611991470893453</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9267317265408955</v>
+        <v>0.8661405325967889</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9658718521337769</v>
+        <v>0.9475909058575106</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.814564799818952</v>
+        <v>0.7223088486803995</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8952149339162746</v>
+        <v>0.8363127746495439</v>
       </c>
     </row>
     <row r="5">
@@ -684,52 +684,52 @@
         <v>0.4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9520203711062279</v>
+        <v>0.8955270766895271</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9794626985353913</v>
+        <v>0.9612193459982027</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8838552827833505</v>
+        <v>0.8054230943330157</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9381901868228555</v>
+        <v>0.8901675762936124</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9386683571831695</v>
+        <v>0.8817755533115351</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9734961549725154</v>
+        <v>0.9560874882994432</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7814467174365831</v>
+        <v>0.6736150753332011</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8709999033049685</v>
+        <v>0.8043098610208018</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9274995342571701</v>
+        <v>0.8716199683072219</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9671683328594083</v>
+        <v>0.9511194168455799</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7837767853474055</v>
+        <v>0.6791320424853569</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8771362469091919</v>
+        <v>0.8113687742963717</v>
       </c>
       <c r="O5" t="n">
-        <v>0.947961595882905</v>
+        <v>0.8913574979433222</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9773918752910944</v>
+        <v>0.9593814696035912</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8703355171623297</v>
+        <v>0.7845810276268561</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9286073053416932</v>
+        <v>0.8755310134454996</v>
       </c>
     </row>
     <row r="6">
@@ -740,52 +740,52 @@
         <v>0.5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9617213474949984</v>
+        <v>0.9112205808593395</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9844086444253333</v>
+        <v>0.9683919044265497</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9142878383954732</v>
+        <v>0.8457363920937264</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9551479842369736</v>
+        <v>0.9142284265234112</v>
       </c>
       <c r="G6" t="n">
-        <v>0.955538707538991</v>
+        <v>0.904147261015268</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9818311142734599</v>
+        <v>0.9659421153688539</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8379014105071043</v>
+        <v>0.7427721003872929</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9053197809497419</v>
+        <v>0.8476910188858253</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9487235180952455</v>
+        <v>0.8972149314580639</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9783269787219063</v>
+        <v>0.9628595670735663</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8377311889887873</v>
+        <v>0.7454671132660069</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9087666255541856</v>
+        <v>0.8521584468884801</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9595801874651213</v>
+        <v>0.9088830010716865</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9833907935773738</v>
+        <v>0.9674289338168118</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9050366986257488</v>
+        <v>0.8308611743380186</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9485967170218669</v>
+        <v>0.9038560840438746</v>
       </c>
     </row>
     <row r="7">
@@ -796,52 +796,52 @@
         <v>0.6</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9678380625574911</v>
+        <v>0.9223604264088705</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9872762060676193</v>
+        <v>0.9733014386060579</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9354936750674947</v>
+        <v>0.8760276469075715</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9667323066054202</v>
+        <v>0.9320398630479104</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9644198646201376</v>
+        <v>0.918815417814824</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9859909191389291</v>
+        <v>0.9722309186957349</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8827980877190941</v>
+        <v>0.804725670816099</v>
       </c>
       <c r="J7" t="n">
-        <v>0.932764648953159</v>
+        <v>0.8865129294281197</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9602930788692629</v>
+        <v>0.9148329764962265</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9839669421597228</v>
+        <v>0.9705659384724528</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8818472890434546</v>
+        <v>0.8046540535697296</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9344624186362039</v>
+        <v>0.8884339266475623</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9666445586373235</v>
+        <v>0.9211758625651283</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9867398410351909</v>
+        <v>0.9728492306549761</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9291836251062204</v>
+        <v>0.8656231901186107</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9623545342986591</v>
+        <v>0.9249566928629166</v>
       </c>
     </row>
     <row r="8">
@@ -852,52 +852,52 @@
         <v>0.7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9731242638509572</v>
+        <v>0.9362223112831218</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9900676014100429</v>
+        <v>0.9799327081967881</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9536762230458361</v>
+        <v>0.9057481911096693</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9769579659563143</v>
+        <v>0.9502875748456745</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9715928537007139</v>
+        <v>0.9344346609915014</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9894912462538296</v>
+        <v>0.9793870309092018</v>
       </c>
       <c r="I8" t="n">
-        <v>0.919568855102964</v>
+        <v>0.8594195812053106</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9560119596595511</v>
+        <v>0.9218058855766362</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9696062377955968</v>
+        <v>0.9323213496433814</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9886243499212045</v>
+        <v>0.9786503871624893</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9188523385099755</v>
+        <v>0.8593215705152633</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9568886498458106</v>
+        <v>0.9230379442894541</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9724219028291685</v>
+        <v>0.9355157811692179</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9897757454332947</v>
+        <v>0.9796942146409627</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9499099647169861</v>
+        <v>0.8993201929008744</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9744035023740861</v>
+        <v>0.9459559209408821</v>
       </c>
     </row>
     <row r="9">
@@ -908,52 +908,52 @@
         <v>0.8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9781603090893333</v>
+        <v>0.9499952182545151</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9918620946345846</v>
+        <v>0.9839964319283551</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9670718580673481</v>
+        <v>0.9329843343402023</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9835761715000749</v>
+        <v>0.9650346534476181</v>
       </c>
       <c r="G9" t="n">
-        <v>0.977346452276369</v>
+        <v>0.9491074826479622</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9916020654257975</v>
+        <v>0.9837902748757057</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9503908958763359</v>
+        <v>0.9077969997669356</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9735157656727</v>
+        <v>0.9497581930087362</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9764361300909611</v>
+        <v>0.9482044372848296</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9911971719051966</v>
+        <v>0.9834035239291621</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9496623689593044</v>
+        <v>0.9074064478597249</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9736819821018609</v>
+        <v>0.9501669505915424</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9777357325549186</v>
+        <v>0.9495914948883448</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9916864973925098</v>
+        <v>0.9838687943751721</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9652400114361692</v>
+        <v>0.929829607340684</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9823644809071537</v>
+        <v>0.9629735733429223</v>
       </c>
     </row>
     <row r="10">
@@ -964,52 +964,52 @@
         <v>0.9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9869086760367309</v>
+        <v>0.9685156032209097</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9960671559638264</v>
+        <v>0.9924360067142063</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9829006293307393</v>
+        <v>0.9624795842788236</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9924543820242255</v>
+        <v>0.9823892957150209</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9868818521927661</v>
+        <v>0.96851397468963</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9960591751045694</v>
+        <v>0.9924375077892085</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9775943320631155</v>
+        <v>0.954890005825073</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9895158370379912</v>
+        <v>0.9781709406375321</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9865401608676795</v>
+        <v>0.9682527846925739</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9959393277463803</v>
+        <v>0.9923512965395234</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9773877888328908</v>
+        <v>0.9548052290446294</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9896085552182792</v>
+        <v>0.9783875016503039</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9867572806419348</v>
+        <v>0.9684074604326807</v>
       </c>
       <c r="P10" t="n">
-        <v>0.996013225416284</v>
+        <v>0.9924029005722103</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.982326165707459</v>
+        <v>0.9612091082717877</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9920712752254092</v>
+        <v>0.9815829739341981</v>
       </c>
     </row>
   </sheetData>
